--- a/InputData/bldgs/PPEIdtIL/Potential Perc Eff Improvement due to Impr Labeling.xlsx
+++ b/InputData/bldgs/PPEIdtIL/Potential Perc Eff Improvement due to Impr Labeling.xlsx
@@ -1,26 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rorvis\Dropbox (Energy InNovation)\My Documents\Energy Policy Solutions\US\Models\eps-us\InputData\bldgs\PPEIdtIL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\EPS Structure Research\eps-us-dc-replay\InputData\bldgs\PPEIdtIL\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E227C8A-E665-4C26-BC63-653038D0ADBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="30" windowWidth="24915" windowHeight="11055" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="PPEIdtIL" sheetId="3" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>Source:</t>
   </si>
@@ -107,12 +121,21 @@
   </si>
   <si>
     <t>Efficiency Improvement by Building Component (dimensionless)</t>
+  </si>
+  <si>
+    <t>Data Centers</t>
+  </si>
+  <si>
+    <t>Data centers</t>
+  </si>
+  <si>
+    <t>Data centers are a separate building type. They use the commercial values, so the data-centers column copies the commercial column.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -166,7 +189,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -179,6 +202,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -199,9 +225,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -239,9 +265,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -276,7 +302,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -311,7 +337,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -484,8 +510,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B22"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -561,34 +587,42 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>18</v>
       </c>
     </row>
+    <row r="24" spans="1:2" ht="300" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1"/>
+    <hyperlink ref="B6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
@@ -596,11 +630,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.28515625" customWidth="1"/>
@@ -609,7 +643,7 @@
     <col min="4" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>28</v>
       </c>
@@ -622,8 +656,11 @@
       <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -637,8 +674,12 @@
       <c r="D2">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2">
+        <f>$D2</f>
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -652,8 +693,12 @@
       <c r="D3">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3">
+        <f>$D3</f>
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -667,8 +712,12 @@
       <c r="D4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4">
+        <f>$D4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -682,8 +731,12 @@
       <c r="D5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E5">
+        <f>$D5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -697,8 +750,12 @@
       <c r="D6">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6">
+        <f>$D6</f>
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -710,6 +767,10 @@
         <v>0</v>
       </c>
       <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <f>$D7</f>
         <v>0</v>
       </c>
     </row>
